--- a/economia/saida/Economia_Rede_Nexus.xlsx
+++ b/economia/saida/Economia_Rede_Nexus.xlsx
@@ -495,7 +495,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>223</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>949</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>10.475</t>
+          <t>10.832</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>89,72 bi</t>
+          <t>167,33 bi</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>0,2414</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0,241</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>0,314</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0,408</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>0,689</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>0,896</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>1,165</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>1,515</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>1,969</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Proposta: 1 chave a cada 5.000 blocos (13 por hora na mina 1 sem encantamento). Os 0,10% de hoje dariam 67/h e, com área, centenas</t>
+          <t>Mantido o valor de hoje (Enzo, 21/10). Atenção: blocos de área também rolam chave, então com área sobe bastante</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Proposta: liberar um encantamento de área (comprar o nível 1) custa 1 h de renda de quem está nesse ponto do jogo</t>
+          <t>Proposta: liberar um encantamento de área (nível 1) custa 6 min de renda de quem está nesse ponto. Com 1 h ninguém liberava os últimos</t>
         </is>
       </c>
     </row>
@@ -1343,19 +1343,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Proposta: a picareta (EXP) anda 10% à frente do nível típico dos encantamentos, para travar só quem pula a mineração</t>
+          <t>Proposta: a picareta (EXP) anda 10% à frente do jogador típico. Hoje ela só serve para liberar os encantamentos</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>design.fracao_do_tempo_por_atividade</t>
+          <t>design.faixas_preco</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>[{"mina": 1.0, "agricultura": 0.0, "combate": 0.0}, {"mina":</t>
+          <t>[[0, 0], [1, 10], [11, 50], [51, 100], [101, 250], [251, 500</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1365,19 +1365,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Proposta: como o jogador ativo divide o tempo em cada rank (Cidadão primeiro). Os requisitos de rank (cabeças, fragmentos) forçam isso</t>
+          <t>Formato que o Enzo já usava (0-10, 11-50 ... 901-1000), com o nível 0 separado (liberar o encantamento custa mais)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>design.fracao_money_para_picareta</t>
+          <t>design.fracao_do_tempo_por_atividade</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>[{"mina": 1.0, "agricultura": 0.0, "combate": 0.0}, {"mina":</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1387,19 +1387,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Proposta: o jogador típico gasta metade do money na picareta e metade em rank. Define o peso das gemas (esforço 50/50)</t>
+          <t>Proposta: como o jogador ativo divide o tempo em cada rank (Cidadão primeiro). Os requisitos de rank (cabeças, fragmentos) forçam isso</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>design.fragmento_mineracao_chance_pct</t>
+          <t>design.fracao_money_para_picareta</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>0.0015</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1409,19 +1409,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Proposta: 1 Fragmento de Mineração a cada ~67.000 blocos (1 por hora de mina pura). Só cai minerando de verdade</t>
+          <t>Proposta: o jogador típico gasta metade do money na picareta e metade em rank. Define o peso das gemas (esforço 50/50)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>design.money_agricultura_vs_mina</t>
+          <t>design.fragmento_mineracao_chance_pct</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Proposta: média das plantações em money (Fungo 70%, Cana 45%, Cenoura e Melancia menos). Sai do bloco agricultura</t>
+          <t>Proposta: 1 Fragmento de Mineração a cada ~67.000 blocos (1 por hora de mina pura). Só cai minerando de verdade</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>design.payback_horas_fim</t>
+          <t>design.money_agricultura_vs_mina</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1453,19 +1453,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Proposta calibrada no simulador: com 10 h no fim, gastar 20% ou 80% do money na picareta dá quase o mesmo tempo (nenhuma estratégia muito melhor). Com 25 h, correr para o rank ficava 16% mais rápido</t>
+          <t>Proposta: média das plantações em money (Fungo 70%, Cana 45%, Cenoura e Melancia menos). Sai do bloco agricultura</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>design.payback_horas_inicio</t>
+          <t>design.payback_horas_fim</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -1475,19 +1475,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Proposta: no começo do jogo um upgrade se paga em 15 min de mineração</t>
+          <t>Proposta calibrada no simulador: com 10 h no fim, gastar 20% ou 80% do money na picareta dá quase o mesmo tempo (nenhuma estratégia muito melhor). Com 25 h, correr para o rank ficava 16% mais rápido</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>design.peso_horas_por_rank</t>
+          <t>design.payback_horas_inicio</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>[5, 8, 12, 16, 20, 24, 28, 33, 38, 46]</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1497,19 +1497,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Proposta: horas do jogador ativo em cada rank (soma 230). Começo rápido, final pesado</t>
+          <t>Proposta: no começo do jogo um upgrade se paga em 15 min de mineração</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>design.picareta_max_na_fracao</t>
+          <t>design.peso_horas_por_rank</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>[5, 8, 12, 16, 20, 24, 28, 33, 38, 46]</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Proposta: o jogador típico chega no Dragão X com a picareta perto do nível 750. Picareta 1000 e tudo no máximo levam 50% a mais (prestígios)</t>
+          <t>Proposta: horas do jogador ativo em cada rank (soma 230). Começo rápido, final pesado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>design.prestigio_crescimento</t>
+          <t>design.picareta_max_na_fracao</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -1541,19 +1541,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Proposta: cada prestígio seguinte custa 30% a mais que o anterior (a picareta continua crescendo)</t>
+          <t>Proposta: o jogador típico chega no Dragão X com os encantamentos perto de 850 a 900. O 1000 fica para os prestígios</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>design.prestigio_horas_cada</t>
+          <t>design.prestigio_crescimento</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -1563,19 +1563,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Proposta: a 1a volta de prestígio leva ~35 h de um jogador ativo com a picareta que já tem</t>
+          <t>Proposta: cada prestígio seguinte custa 30% a mais que o anterior (a picareta continua crescendo)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>design.razao_gemas_entre_minas</t>
+          <t>design.prestigio_horas_cada</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -1585,19 +1585,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Proposta: gemas crescem mais devagar para os números de gemas ficarem legíveis. Os preços em gemas acompanham</t>
+          <t>Proposta: a 1a volta de prestígio leva ~35 h de um jogador ativo com a picareta que já tem</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>design.razao_money_entre_minas</t>
+          <t>design.razao_gemas_entre_minas</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -1607,19 +1607,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Proposta: cada mina nova paga 2,5x a anterior (salto que o jogador sente; a antiga do ChatGPT também subia ~2,5x)</t>
+          <t>Proposta: gemas crescem mais devagar para os números de gemas ficarem legíveis. Os preços em gemas acompanham</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>encantamentos_area</t>
+          <t>design.razao_money_entre_minas</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"Explosivo": {"contribuicao": 0.3, "blocos": 27, "radios": </t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -1629,19 +1629,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Proposta. Blocos: produto das medidas do radios atual (Cruz, Laser, Fenda e Chuva superestimados de propósito, o lado seguro). Validar: ativar cada um numa parede e contar</t>
+          <t>Proposta: cada mina nova paga 2,5x a anterior (salto que o jogador sente; a antiga do ChatGPT também subia ~2,5x)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>escala_area_por_faixa</t>
+          <t>encantamentos_area</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>{"1-250": 0.5, "251-500": 0.67, "501-750": 0.83, "751-1000":</t>
+          <t xml:space="preserve">{"Explosivo": {"contribuicao": 0.3, "blocos": 27, "radios": </t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -1651,41 +1651,41 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Proposta: a área cresce nos marcos 250/500/750/1000 até o tamanho que vocês já usam hoje</t>
+          <t>Proposta. Blocos: produto das medidas do radios atual (Cruz, Laser, Fenda e Chuva superestimados de propósito, o lado seguro). Validar: ativar cada um numa parede e contar</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>metas.horas_ativo_total</t>
+          <t>escala_area_por_faixa</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>decidido</t>
+          <t>{"1-1000": 1.0}</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>hipotese</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre, seção 2: 220 a 240 horas efetivas para um jogador ativo terminar</t>
+          <t>Enzo (21/10) pediu formato simples: área igual à de hoje do nível 1 ao 1000; só a chance sobe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>metas.perfis</t>
+          <t>metas.horas_ativo_total</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>{"casual": {"horas_dia": 1.5, "semanas_min": 12, "semanas_ma</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1695,41 +1695,41 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre, seção 2 (tabela de perfis)</t>
+          <t>Prompt mestre, seção 2: 220 a 240 horas efetivas para um jogador ativo terminar</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>mina.blocos_total</t>
+          <t>metas.perfis</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>751060</t>
+          <t>{"casual": {"horas_dia": 1.5, "semanas_min": 12, "semanas_ma</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>medido</t>
+          <t>decidido</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>MinaReset/minas.yml: 94 x 85 x 94 = 751.060 (todas as minas de rank)</t>
+          <t>Prompt mestre, seção 2 (tabela de perfis)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>mina.camada_blocos</t>
+          <t>mina.blocos_total</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>751060</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1739,19 +1739,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>MinaReset/minas.yml: uma camada 94 x 94</t>
+          <t>MinaReset/minas.yml: 94 x 85 x 94 = 751.060 (todas as minas de rank)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>mina.chance_chave_atual_pct</t>
+          <t>mina.camada_blocos</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1761,19 +1761,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>MinaReset/blocos.yml e Enzo (21/10): 0,10% por bloco quebrado</t>
+          <t>MinaReset/minas.yml: uma camada 94 x 94</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>mina.reset_porcentagem</t>
+          <t>mina.chance_chave_atual_pct</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>MinaReset/minas.yml, porcentagem: 40 (reseta ao quebrar 40%)</t>
+          <t>MinaReset/blocos.yml e Enzo (21/10): 0,10% por bloco quebrado</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>mina.reset_segundos</t>
+          <t>mina.reset_porcentagem</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1805,36 +1805,36 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>MinaReset/minas.yml, reset: 1200</t>
+          <t>MinaReset/minas.yml, porcentagem: 40 (reseta ao quebrar 40%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>minas.mina1_gemas_por_bloco</t>
+          <t>mina.reset_segundos</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>decidido</t>
+          <t>medido</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre 3.1 e Enzo (21/10)</t>
+          <t>MinaReset/minas.yml, reset: 1200</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>minas.mina1_money_por_bloco</t>
+          <t>minas.mina1_gemas_por_bloco</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -1849,19 +1849,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre 3.1 e Enzo (21/10): mina Cidadão paga 1 money e 1 gema</t>
+          <t>Prompt mestre 3.1 e Enzo (21/10)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>minas.uma_por_rank</t>
+          <t>minas.mina1_money_por_bloco</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1871,19 +1871,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): no rank Cidadão minera na mina Cidadão, e assim por diante</t>
+          <t>Prompt mestre 3.1 e Enzo (21/10): mina Cidadão paga 1 money e 1 gema</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>minas.vip_multiplicador_da_mina_cidadao</t>
+          <t>minas.uma_por_rank</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1893,41 +1893,41 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): a mina VIP paga o dobro da mina normal (que paga 1 money e 1 gema)</t>
+          <t>Enzo (21/10): no rank Cidadão minera na mina Cidadão, e assim por diante</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>mineracao.area_dispara_outro_encantamento</t>
+          <t>minas.vip_multiplicador_da_mina_cidadao</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>medido</t>
+          <t>decidido</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Enzo, teste 1 (21/10/2026): Cruz não saiu do meio de uma explosão. Só 1 teste, repetir se der</t>
+          <t>Enzo (21/10): a mina VIP paga o dobro da mina normal (que paga 1 money e 1 gema)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>mineracao.area_paga_bloco_inteiro</t>
+          <t>mineracao.area_dispara_outro_encantamento</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1937,19 +1937,19 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Enzo, teste 2 (21/10/2026): bloco quebrado pela explosão paga</t>
+          <t>Enzo, teste 1 (21/10/2026): Cruz não saiu do meio de uma explosão. Só 1 teste, repetir se der</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>mineracao.blocos_por_hora</t>
+          <t>mineracao.area_paga_bloco_inteiro</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1959,19 +1959,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Enzo, teste na mina Cidadão: 5.620 blocos em 5 min com picareta padrão sem Fortuna</t>
+          <t>Enzo, teste 2 (21/10/2026): bloco quebrado pela explosão paga</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>mineracao.fly_multiplicador</t>
+          <t>mineracao.blocos_por_hora</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>67440</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1981,19 +1981,19 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Enzo, teste com Fly: igual ou pior que sem Fly</t>
+          <t>Enzo, teste na mina Cidadão: 5.620 blocos em 5 min com picareta padrão sem Fortuna</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>picareta.exp_aumento</t>
+          <t>mineracao.fly_multiplicador</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2003,85 +2003,85 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Encantamentos/evolutivos.yml, picareta aumento (lido como +39 de EXP por nível, ver hipoteses)</t>
+          <t>Enzo, teste com Fly: igual ou pior que sem Fly</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>picareta.exp_em_todas_as_minas</t>
+          <t>picareta.exp_aumento</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>decidido</t>
+          <t>medido</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): a picareta ganha EXP em todas as minas, não igualmente</t>
+          <t>Encantamentos/evolutivos.yml, picareta aumento (lido como +39 de EXP por nível, ver hipoteses)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>picareta.exp_inicial</t>
+          <t>picareta.exp_em_todas_as_minas</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>medido</t>
+          <t>decidido</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Encantamentos/evolutivos.yml, picareta exp-inicial</t>
+          <t>Enzo (21/10): a picareta ganha EXP em todas as minas, não igualmente</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>picareta.fortuna_pct_por_nivel</t>
+          <t>picareta.exp_inicial</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>decidido</t>
+          <t>medido</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre 6.1: +0,30% de money por nível (+300% no 1.000). Referência mais recente</t>
+          <t>Encantamentos/evolutivos.yml, picareta exp-inicial</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>picareta.gemado_pct_por_nivel</t>
+          <t>picareta.fortuna_pct_por_nivel</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2091,19 +2091,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre 6.2: +0,20% de gemas por nível (+200% no 1.000)</t>
+          <t>Prompt mestre 6.1: +0,30% de money por nível (+300% no 1.000). Referência mais recente</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>picareta.multiplicador_prisma</t>
+          <t>picareta.gemado_pct_por_nivel</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2113,19 +2113,19 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): não existe Multiplicador de Prisma, remover</t>
+          <t>Prompt mestre 6.2: +0,20% de gemas por nível (+200% no 1.000)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>picareta.niveis_maximos</t>
+          <t>picareta.multiplicador_prisma</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>{"speed": 2, "haste": 2, "fortuna": 1000, "gemado": 1000, "c</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2135,19 +2135,19 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre, seção 6: 16 encantamentos</t>
+          <t>Enzo (21/10): não existe Multiplicador de Prisma, remover</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>picareta.usar_booster_money_em_armadura</t>
+          <t>picareta.niveis_maximos</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>{"speed": 2, "haste": 2, "fortuna": 1000, "gemado": 1000, "c</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2157,63 +2157,63 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): não vamos usar booster de money. A Fortuna Aprimorada da picareta continua (é ela que dá o +money)</t>
+          <t>Prompt mestre, seção 6: 16 encantamentos</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>plantacoes</t>
+          <t>picareta.usar_booster_money_em_armadura</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>{"fungo": {"libera_rank": 20, "money_vs_mina": 0.7, "semente</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>hipotese</t>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>decidido</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Proposta. libera_rank: posição 0 a 99 (20 = Guerreiro I). money_vs_mina: renda em money comparada com minerar no mesmo rank</t>
+          <t>Enzo (21/10): não vamos usar booster de money. A Fortuna Aprimorada da picareta continua (é ela que dá o +money)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>ranks.nomes</t>
+          <t>plantacoes</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>["Cidadão", "Explorador", "Guerreiro", "Tritão", "Guardião",</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>decidido</t>
+          <t>{"fungo": {"libera_rank": 20, "money_vs_mina": 0.7, "semente</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>hipotese</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre, seção 4: 10 ranks com níveis I a X</t>
+          <t>Proposta. libera_rank: posição 0 a 99 (20 = Guerreiro I). money_vs_mina: renda em money comparada com minerar no mesmo rank</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>ranks.prestigio_reseta</t>
+          <t>ranks.nomes</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>{"rank": true, "picareta": false, "dinheiro": false}</t>
+          <t>["Cidadão", "Explorador", "Guerreiro", "Tritão", "Guardião",</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2223,19 +2223,19 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10/2026): prestígio dá +1 prestígio e reseta os ranks; picareta e dinheiro não</t>
+          <t>Prompt mestre, seção 4: 10 ranks com níveis I a X</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>ranks.prestigios</t>
+          <t>ranks.prestigio_reseta</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>{"rank": true, "picareta": false, "dinheiro": false}</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2245,19 +2245,19 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Enzo (20/10/2026): sem temporadas, precisa de prestígio no final. Quantidade proposta: 10</t>
+          <t>Enzo (21/10/2026): prestígio dá +1 prestígio e reseta os ranks; picareta e dinheiro não</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>regras.item_preso_na_conta</t>
+          <t>ranks.prestigios</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Enzo (20/10): não queremos item preso à conta</t>
+          <t>Enzo (20/10/2026): sem temporadas, precisa de prestígio no final. Quantidade proposta: 10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>regras.limite_diario</t>
+          <t>regras.item_preso_na_conta</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -2289,19 +2289,19 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): não tem limite diário</t>
+          <t>Enzo (20/10): não queremos item preso à conta</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>regras.multicontas_permitidas</t>
+          <t>regras.limite_diario</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2311,19 +2311,19 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): pode ter várias contas por jogador, conta fake e tudo mais</t>
+          <t>Enzo (21/10): não tem limite diário</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>regras.taxa_pay_leilao</t>
+          <t>regras.multicontas_permitidas</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2333,14 +2333,14 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Enzo (20/10): sem taxa no /pay e no leilão</t>
+          <t>Enzo (21/10): pode ter várias contas por jogador, conta fake e tudo mais</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>servidor.blocos_area_dao_exp</t>
+          <t>regras.taxa_pay_leilao</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -2348,26 +2348,26 @@
           <t>False</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>hipotese</t>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>decidido</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Conservador: o modelo conta EXP só do bloco que o jogador quebra. Se a área também der EXP, a picareta sobe mais rápido (trava mais frouxa, sem risco de inflação)</t>
+          <t>Enzo (20/10): sem taxa no /pay e no leilão</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>servidor.blocos_area_rolam_chave</t>
+          <t>servidor.blocos_area_dao_exp</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -2377,14 +2377,14 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Enzo (21/10): cada bloco quebrado tem chance de chave. Validar contando chaves com e sem Explosivo</t>
+          <t>Conservador: o modelo conta EXP só do bloco que o jogador quebra. Se a área também der EXP, a picareta sobe mais rápido (trava mais frouxa, sem risco de inflação)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>servidor.booster_soma_porcentagem</t>
+          <t>servidor.blocos_area_rolam_chave</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -2399,19 +2399,19 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Placeholder %ghostencantamentos_booster_money% = 300 vira +300%. Validar: Fortuna Aprimorada 1000, quebrar 100 blocos na mina 1, deve dar 400</t>
+          <t>Enzo (21/10): cada bloco quebrado tem chance de chave. Validar contando chaves com e sem Explosivo</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>servidor.cana_quebras_por_hora</t>
+          <t>servidor.booster_soma_porcentagem</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Não medido. Crescimento 90 s. Validar: 1 min colhendo</t>
+          <t>Placeholder %ghostencantamentos_booster_money% = 300 vira +300%. Validar: Fortuna Aprimorada 1000, quebrar 100 blocos na mina 1, deve dar 400</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>servidor.cenoura_quebras_por_hora</t>
+          <t>servidor.cana_quebras_por_hora</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>153000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -2443,19 +2443,19 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Prompt mestre 3.4: igual ao Fungo. Validar: 1 min colhendo cenoura</t>
+          <t>Não medido. Crescimento 90 s. Validar: 1 min colhendo</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>servidor.chance_em_porcentagem</t>
+          <t>servidor.cenoura_quebras_por_hora</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>153000</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Encantamentos de combate usam 100 = sempre; ver docs/como-o-plugin-funciona.md 1.1</t>
+          <t>Prompt mestre 3.4: igual ao Fungo. Validar: 1 min colhendo cenoura</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>servidor.exp_aumento_linear</t>
+          <t>servidor.chance_em_porcentagem</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -2487,19 +2487,19 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>EXP para o nível n = 2500 + 39 x n. Validar no menu da picareta (Experiência @exp/@maxexp)</t>
+          <t>Encantamentos de combate usam 100 = sempre; ver docs/como-o-plugin-funciona.md 1.1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>servidor.golpes_por_segundo</t>
+          <t>servidor.exp_aumento_linear</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -2509,19 +2509,19 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Cliques efetivos por segundo num boss. Validar: cronometrar uma luta</t>
+          <t>EXP para o nível n = 2500 + 39 x n. Validar no menu da picareta (Experiência @exp/@maxexp)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>servidor.melancia_quebras_por_hora</t>
+          <t>servidor.golpes_por_segundo</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -2531,19 +2531,19 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Não medido. Crescimento 75 a 100 s (mais lento que fungo). Validar: 1 min colhendo</t>
+          <t>Cliques efetivos por segundo num boss. Validar: cronometrar uma luta</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>servidor.mobs_por_spawn_por_spawner</t>
+          <t>servidor.melancia_quebras_por_hora</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -2553,19 +2553,19 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Cada spawner empilhado solta 1 mob a cada 30 s. Validar: 1 spawner por 5 min, contar mobs</t>
+          <t>Não medido. Crescimento 75 a 100 s (mais lento que fungo). Validar: 1 min colhendo</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>servidor.ocupacao_media_da_mina</t>
+          <t>servidor.mobs_por_spawn_por_spawner</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>A mina reseta ao chegar em 40% quebrada, então fica entre 100% e 60% cheia (média 80%)</t>
+          <t>Cada spawner empilhado solta 1 mob a cada 30 s. Validar: 1 spawner por 5 min, contar mobs</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>servidor.speed_haste_aumentam_producao</t>
+          <t>servidor.ocupacao_media_da_mina</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -2597,19 +2597,19 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Quebra já é instantânea e o Fly não mudou nada no teste. Validar: 5 min com Haste II</t>
+          <t>A mina reseta ao chegar em 40% quebrada, então fica entre 100% e 60% cheia (média 80%)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>servidor.velocidade_igual_em_todas_as_minas</t>
+          <t>servidor.speed_haste_aumentam_producao</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -2619,49 +2619,71 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Picareta tem Eficiência 32.000 (quebra instantânea). Validar: repetir o teste de 5 min na mina Dragão</t>
+          <t>Quebra já é instantânea e o Fly não mudou nada no teste. Validar: 5 min com Haste II</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>spawners.cabecas_por_morte_sem_pilhagem</t>
+          <t>servidor.velocidade_igual_em_todas_as_minas</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>medido</t>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>hipotese</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Spawners/mobs.yml, looting 0: min 1, max 2 (média 1,5)</t>
+          <t>Picareta tem Eficiência 32.000 (quebra instantânea). Validar: repetir o teste de 5 min na mina Dragão</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
+          <t>spawners.cabecas_por_morte_sem_pilhagem</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>medido</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Spawners/mobs.yml, looting 0: min 1, max 2 (média 1,5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
           <t>spawners.tempo_spawn_segundos</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>medido</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Spawners/mobs.yml, tempo-spawn de todos os mobs</t>
         </is>
@@ -2740,7 +2762,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11.400</t>
+          <t>15.600</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2755,7 +2777,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2.752</t>
+          <t>15.600</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2789,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>12.400</t>
+          <t>19.300</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2782,7 +2804,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2.993</t>
+          <t>19.300</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2816,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>15.200</t>
+          <t>22.600</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2809,7 +2831,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>3.669</t>
+          <t>22.600</t>
         </is>
       </c>
     </row>
@@ -2821,12 +2843,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>24.900</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2836,7 +2858,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>3.862</t>
+          <t>24.900</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2870,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>29.000</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2863,7 +2885,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>29.000</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2897,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>19.300</t>
+          <t>31.100</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2890,7 +2912,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>4.659</t>
+          <t>31.100</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2924,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>20.900</t>
+          <t>33.600</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>5.045</t>
+          <t>33.600</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2951,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>22.100</t>
+          <t>36.900</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2944,7 +2966,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>5.335</t>
+          <t>36.900</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2978,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.600</t>
+          <t>39.200</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2971,7 +2993,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>5.697</t>
+          <t>39.200</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3005,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>25.800</t>
+          <t>42.900</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2998,7 +3020,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>6.228</t>
+          <t>42.900</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3032,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>55.200</t>
+          <t>93.200</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3025,7 +3047,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>13.325</t>
+          <t>93.200</t>
         </is>
       </c>
     </row>
@@ -3037,22 +3059,22 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>60.300</t>
+          <t>106.000</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>14.556</t>
+          <t>106.000</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3086,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>70.200</t>
+          <t>127.000</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -3079,7 +3101,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>16.946</t>
+          <t>127.000</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3113,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>76.200</t>
+          <t>138.000</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3106,7 +3128,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>18.395</t>
+          <t>138.000</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3140,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>84.200</t>
+          <t>158.000</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -3133,7 +3155,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>20.326</t>
+          <t>158.000</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3167,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>89.600</t>
+          <t>182.000</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -3160,7 +3182,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>21.629</t>
+          <t>182.000</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3194,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>99.700</t>
+          <t>203.000</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3187,7 +3209,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>24.068</t>
+          <t>203.000</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3221,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>109.000</t>
+          <t>222.000</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3214,7 +3236,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>26.313</t>
+          <t>222.000</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3248,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>114.000</t>
+          <t>227.000</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -3241,7 +3263,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>27.520</t>
+          <t>227.000</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3275,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>127.000</t>
+          <t>244.000</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -3268,7 +3290,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>30.658</t>
+          <t>244.000</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3302,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>229.000</t>
+          <t>447.000</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3295,7 +3317,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>55.281</t>
+          <t>447.000</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3329,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>259.000</t>
+          <t>488.000</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3322,7 +3344,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>62.523</t>
+          <t>488.000</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3356,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>294.000</t>
+          <t>549.000</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3349,7 +3371,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>70.972</t>
+          <t>549.000</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3383,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>331.000</t>
+          <t>615.000</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -3376,7 +3398,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>79.903</t>
+          <t>615.000</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3410,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>359.000</t>
+          <t>686.000</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3403,7 +3425,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>86.663</t>
+          <t>686.000</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3437,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>406.000</t>
+          <t>725.000</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3430,7 +3452,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>98.008</t>
+          <t>725.000</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3464,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>446.000</t>
+          <t>794.000</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3457,7 +3479,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>107.664</t>
+          <t>794.000</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3491,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>487.000</t>
+          <t>851.000</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3484,7 +3506,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>117.562</t>
+          <t>851.000</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3518,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>535.000</t>
+          <t>914.000</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3511,7 +3533,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>129.149</t>
+          <t>914.000</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3545,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>593.000</t>
+          <t>986.000</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3538,7 +3560,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>143.150</t>
+          <t>986.000</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3572,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>862.000</t>
+          <t>1,64 mi</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3565,7 +3587,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>208.087</t>
+          <t>1,64 mi</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3599,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>999.000</t>
+          <t>1,91 mi</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3592,7 +3614,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>241.159</t>
+          <t>1,91 mi</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3626,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>1,12 mi</t>
+          <t>2,12 mi</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3619,7 +3641,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>270.368</t>
+          <t>2,12 mi</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3653,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>1,65 mi</t>
+          <t>2,57 mi</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3646,7 +3668,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>398.310</t>
+          <t>2,57 mi</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3680,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>1,65 mi</t>
+          <t>4,89 mi</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3673,7 +3695,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>398.310</t>
+          <t>4,89 mi</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3707,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>1,65 mi</t>
+          <t>5,32 mi</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3700,7 +3722,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>398.310</t>
+          <t>5,32 mi</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3734,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2,25 mi</t>
+          <t>5,72 mi</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3727,7 +3749,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>543.150</t>
+          <t>5,72 mi</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3761,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>3,64 mi</t>
+          <t>5,82 mi</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3754,7 +3776,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>878.696</t>
+          <t>5,82 mi</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3788,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>4,07 mi</t>
+          <t>5,82 mi</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3781,7 +3803,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>982.498</t>
+          <t>5,82 mi</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3815,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>4,41 mi</t>
+          <t>5,82 mi</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3808,7 +3830,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1,06 mi</t>
+          <t>5,82 mi</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3842,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>6,15 mi</t>
+          <t>5,82 mi</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3835,7 +3857,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1,48 mi</t>
+          <t>5,82 mi</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3869,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>7,10 mi</t>
+          <t>6,51 mi</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3862,7 +3884,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>1,71 mi</t>
+          <t>6,51 mi</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3896,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>7,68 mi</t>
+          <t>7,50 mi</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -3889,7 +3911,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>1,85 mi</t>
+          <t>7,50 mi</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3923,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>7,68 mi</t>
+          <t>8,59 mi</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3916,7 +3938,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>1,85 mi</t>
+          <t>8,59 mi</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3950,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>7,68 mi</t>
+          <t>9,64 mi</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3943,7 +3965,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1,85 mi</t>
+          <t>9,64 mi</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3977,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>7,68 mi</t>
+          <t>11,10 mi</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3970,7 +3992,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>1,85 mi</t>
+          <t>11,10 mi</t>
         </is>
       </c>
     </row>
@@ -3982,12 +4004,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>7,68 mi</t>
+          <t>22,50 mi</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3997,7 +4019,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>1,85 mi</t>
+          <t>22,50 mi</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4031,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>12,60 mi</t>
+          <t>24,10 mi</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -4024,7 +4046,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>3,04 mi</t>
+          <t>24,10 mi</t>
         </is>
       </c>
     </row>
@@ -4036,22 +4058,22 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>14,70 mi</t>
+          <t>24,10 mi</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>3,55 mi</t>
+          <t>24,10 mi</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4085,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>16,10 mi</t>
+          <t>27,10 mi</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -4078,7 +4100,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>3,89 mi</t>
+          <t>27,10 mi</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4112,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>23,80 mi</t>
+          <t>27,10 mi</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -4105,7 +4127,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>5,75 mi</t>
+          <t>27,10 mi</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4139,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>27,40 mi</t>
+          <t>31,70 mi</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4127,12 +4149,12 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>6,61 mi</t>
+          <t>31,70 mi</t>
         </is>
       </c>
     </row>
@@ -4144,22 +4166,22 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>29,30 mi</t>
+          <t>61,10 mi</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>7,07 mi</t>
+          <t>61,10 mi</t>
         </is>
       </c>
     </row>
@@ -4171,12 +4193,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>29,30 mi</t>
+          <t>67,40 mi</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -4186,7 +4208,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>7,07 mi</t>
+          <t>67,40 mi</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4220,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>29,30 mi</t>
+          <t>73,10 mi</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -4213,7 +4235,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>7,07 mi</t>
+          <t>73,10 mi</t>
         </is>
       </c>
     </row>
@@ -4225,22 +4247,22 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>29,30 mi</t>
+          <t>74,30 mi</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>7,07 mi</t>
+          <t>74,30 mi</t>
         </is>
       </c>
     </row>
@@ -4252,22 +4274,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>31,90 mi</t>
+          <t>74,30 mi</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>7,70 mi</t>
+          <t>74,30 mi</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4301,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>51,30 mi</t>
+          <t>93,90 mi</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -4294,7 +4316,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>12,38 mi</t>
+          <t>93,90 mi</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4328,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>56,20 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -4321,7 +4343,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>13,57 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
     </row>
@@ -4333,22 +4355,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>61,40 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>14,82 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
     </row>
@@ -4360,22 +4382,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>87,80 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>21,19 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
     </row>
@@ -4387,22 +4409,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>98,00 mi</t>
+          <t>157,00 mi</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>23,66 mi</t>
+          <t>157,00 mi</t>
         </is>
       </c>
     </row>
@@ -4414,22 +4436,22 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>98,00 mi</t>
+          <t>204,00 mi</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>23,66 mi</t>
+          <t>204,00 mi</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4463,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>98,00 mi</t>
+          <t>208,00 mi</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -4456,7 +4478,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>23,66 mi</t>
+          <t>208,00 mi</t>
         </is>
       </c>
     </row>
@@ -4468,22 +4490,22 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>98,00 mi</t>
+          <t>208,00 mi</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>23,66 mi</t>
+          <t>208,00 mi</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4517,22 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>107,00 mi</t>
+          <t>276,00 mi</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>25,83 mi</t>
+          <t>276,00 mi</t>
         </is>
       </c>
     </row>
@@ -4522,22 +4544,22 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>168,00 mi</t>
+          <t>300,00 mi</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>40,56 mi</t>
+          <t>300,00 mi</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4571,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>185,00 mi</t>
+          <t>321,00 mi</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -4559,12 +4581,12 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>44,66 mi</t>
+          <t>321,00 mi</t>
         </is>
       </c>
     </row>
@@ -4576,22 +4598,22 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>203,00 mi</t>
+          <t>333,00 mi</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>49,00 mi</t>
+          <t>333,00 mi</t>
         </is>
       </c>
     </row>
@@ -4603,22 +4625,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>221,00 mi</t>
+          <t>333,00 mi</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>53,35 mi</t>
+          <t>333,00 mi</t>
         </is>
       </c>
     </row>
@@ -4630,22 +4652,22 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>310,00 mi</t>
+          <t>333,00 mi</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>74,83 mi</t>
+          <t>333,00 mi</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4679,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>310,00 mi</t>
+          <t>345,00 mi</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4672,7 +4694,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>74,83 mi</t>
+          <t>345,00 mi</t>
         </is>
       </c>
     </row>
@@ -4684,22 +4706,22 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>310,00 mi</t>
+          <t>435,00 mi</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>74,83 mi</t>
+          <t>435,00 mi</t>
         </is>
       </c>
     </row>
@@ -4711,22 +4733,22 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>310,00 mi</t>
+          <t>890,00 mi</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>74,83 mi</t>
+          <t>890,00 mi</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4760,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>525,00 mi</t>
+          <t>988,00 mi</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4748,12 +4770,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>126</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>126,73 mi</t>
+          <t>988,00 mi</t>
         </is>
       </c>
     </row>
@@ -4765,22 +4787,22 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>579,00 mi</t>
+          <t>1,04 bi</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>139,77 mi</t>
+          <t>1,04 bi</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4814,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>635,00 mi</t>
+          <t>1,15 bi</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -4802,12 +4824,12 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>153,29 mi</t>
+          <t>1,15 bi</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4841,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>692,00 mi</t>
+          <t>1,24 bi</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -4829,12 +4851,12 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>167,05 mi</t>
+          <t>1,24 bi</t>
         </is>
       </c>
     </row>
@@ -4846,22 +4868,22 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>715,00 mi</t>
+          <t>1,28 bi</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>172,60 mi</t>
+          <t>1,28 bi</t>
         </is>
       </c>
     </row>
@@ -4873,22 +4895,22 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>715,00 mi</t>
+          <t>1,28 bi</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>172,60 mi</t>
+          <t>1,28 bi</t>
         </is>
       </c>
     </row>
@@ -4900,22 +4922,22 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>715,00 mi</t>
+          <t>1,28 bi</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>172,60 mi</t>
+          <t>1,28 bi</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4949,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>799,00 mi</t>
+          <t>1,34 bi</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -4937,12 +4959,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>192,88 mi</t>
+          <t>1,34 bi</t>
         </is>
       </c>
     </row>
@@ -4954,22 +4976,22 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>1,51 bi</t>
+          <t>2,20 bi</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>364,51 mi</t>
+          <t>2,20 bi</t>
         </is>
       </c>
     </row>
@@ -4981,22 +5003,22 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>1,69 bi</t>
+          <t>3,43 bi</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>407,97 mi</t>
+          <t>3,43 bi</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5030,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>1,84 bi</t>
+          <t>3,73 bi</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -5018,12 +5040,12 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>444,18 mi</t>
+          <t>3,73 bi</t>
         </is>
       </c>
     </row>
@@ -5035,22 +5057,22 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2,00 bi</t>
+          <t>4,02 bi</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>165</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>482,80 mi</t>
+          <t>4,02 bi</t>
         </is>
       </c>
     </row>
@@ -5062,22 +5084,22 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2,13 bi</t>
+          <t>4,40 bi</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>514,18 mi</t>
+          <t>4,40 bi</t>
         </is>
       </c>
     </row>
@@ -5089,22 +5111,22 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2,28 bi</t>
+          <t>4,68 bi</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>550,39 mi</t>
+          <t>4,68 bi</t>
         </is>
       </c>
     </row>
@@ -5116,22 +5138,22 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2,40 bi</t>
+          <t>4,98 bi</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,63</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>579,36 mi</t>
+          <t>4,98 bi</t>
         </is>
       </c>
     </row>
@@ -5143,22 +5165,22 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2,49 bi</t>
+          <t>4,98 bi</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>601,09 mi</t>
+          <t>4,98 bi</t>
         </is>
       </c>
     </row>
@@ -5170,22 +5192,22 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>4,59 bi</t>
+          <t>4,98 bi</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>186</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>1,11 bi</t>
+          <t>4,98 bi</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5219,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>5,11 bi</t>
+          <t>9,20 bi</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -5207,12 +5229,12 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>1,23 bi</t>
+          <t>9,20 bi</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5246,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>5,64 bi</t>
+          <t>11,40 bi</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -5234,12 +5256,12 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>194</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>1,36 bi</t>
+          <t>11,40 bi</t>
         </is>
       </c>
     </row>
@@ -5251,22 +5273,22 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>6,07 bi</t>
+          <t>12,70 bi</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>1,47 bi</t>
+          <t>12,70 bi</t>
         </is>
       </c>
     </row>
@@ -5278,22 +5300,22 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>6,62 bi</t>
+          <t>13,70 bi</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>1,60 bi</t>
+          <t>13,70 bi</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5327,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>7,55 bi</t>
+          <t>15,00 bi</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -5315,12 +5337,12 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>1,82 bi</t>
+          <t>15,00 bi</t>
         </is>
       </c>
     </row>
@@ -5332,22 +5354,22 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>8,57 bi</t>
+          <t>16,30 bi</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>2,07 bi</t>
+          <t>16,30 bi</t>
         </is>
       </c>
     </row>
@@ -5359,22 +5381,22 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>9,76 bi</t>
+          <t>17,70 bi</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>2,36 bi</t>
+          <t>17,70 bi</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5408,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>11,00 bi</t>
+          <t>19,00 bi</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -5396,12 +5418,12 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>2,66 bi</t>
+          <t>19,00 bi</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5435,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>11,00 bi</t>
+          <t>19,00 bi</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -5423,12 +5445,12 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>2,66 bi</t>
+          <t>19,00 bi</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5869,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -5884,17 +5906,17 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>199.026</t>
+          <t>204.614</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>121.683</t>
+          <t>124.262</t>
         </is>
       </c>
     </row>
@@ -5921,17 +5943,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>583.605</t>
+          <t>618.251</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>220.549</t>
+          <t>231.195</t>
         </is>
       </c>
     </row>
@@ -5958,17 +5980,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1,77 mi</t>
+          <t>1,93 mi</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>413.975</t>
+          <t>446.218</t>
         </is>
       </c>
     </row>
@@ -5995,17 +6017,17 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>5,50 mi</t>
+          <t>6,21 mi</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>798.092</t>
+          <t>888.204</t>
         </is>
       </c>
     </row>
@@ -6032,17 +6054,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>17,29 mi</t>
+          <t>20,22 mi</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1,57 mi</t>
+          <t>1,80 mi</t>
         </is>
       </c>
     </row>
@@ -6069,17 +6091,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>55,05 mi</t>
+          <t>66,66 mi</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3,12 mi</t>
+          <t>3,71 mi</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6128,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>176,96 mi</t>
+          <t>222,85 mi</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>6,28 mi</t>
+          <t>7,79 mi</t>
         </is>
       </c>
     </row>
@@ -6143,17 +6165,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>578,90 mi</t>
+          <t>762,47 mi</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>12,92 mi</t>
+          <t>16,76 mi</t>
         </is>
       </c>
     </row>
@@ -6180,17 +6202,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1,93 bi</t>
+          <t>2,59 bi</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>27,09 mi</t>
+          <t>35,87 mi</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6239,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -6226,7 +6248,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Blocos por hora (medido): 67.440. Chaves por hora sem encantamento: 13.</t>
+          <t>Blocos por hora (medido): 67.440. Chaves por hora sem encantamento: 67.</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6272,7 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6314,7 +6336,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -6378,12 +6400,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6410,12 +6432,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>146</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -6442,12 +6464,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>263</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -6474,12 +6496,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>7.940</t>
+          <t>4.018</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.156</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -6506,12 +6528,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>768.000</t>
+          <t>237.846</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>42.500</t>
+          <t>18.898</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -6538,12 +6560,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>56,60 mi</t>
+          <t>10,96 mi</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>1,02 mi</t>
+          <t>306.832</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -6570,12 +6592,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>59,60 mi</t>
+          <t>471,00 mi</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1,06 mi</t>
+          <t>8,24 mi</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -6602,12 +6624,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6639,7 +6661,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -6666,12 +6688,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6698,12 +6720,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -6730,12 +6752,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>157</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -6762,12 +6784,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>6.170</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>1.480</t>
+          <t>934</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -6794,12 +6816,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>640.000</t>
+          <t>197.970</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>35.400</t>
+          <t>15.880</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -6826,12 +6848,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>49,10 mi</t>
+          <t>9,53 mi</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>880.000</t>
+          <t>265.836</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -6858,12 +6880,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>51,70 mi</t>
+          <t>419,00 mi</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>916.000</t>
+          <t>7,32 mi</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -6890,12 +6912,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -6922,12 +6944,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -6954,12 +6976,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -6986,12 +7008,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -7018,12 +7040,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -7050,12 +7072,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -7082,12 +7104,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>64.000</t>
+          <t>19.640</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -7114,12 +7136,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>5,26 mi</t>
+          <t>1,02 mi</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>94.200</t>
+          <t>28.394</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -7146,12 +7168,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>5,54 mi</t>
+          <t>47,10 mi</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>98.200</t>
+          <t>823.934</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -7178,17 +7200,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>67.700</t>
+          <t>6.770</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>135.000</t>
+          <t>13.500</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>0.00469% por bloco, ~6 blocos</t>
+          <t>0.00139% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -7210,7 +7232,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -7220,7 +7242,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>0.00937% por bloco, ~6 blocos</t>
+          <t>0.00278% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -7242,17 +7264,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>0.04687% por bloco, ~6 blocos</t>
+          <t>0.01389% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -7274,17 +7296,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>0.23438% por bloco, ~6 blocos</t>
+          <t>0.06944% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -7306,17 +7328,17 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>0.46875% por bloco, ~6 blocos</t>
+          <t>0.13889% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -7338,17 +7360,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>1.070</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1.17188% por bloco, ~6 blocos</t>
+          <t>0.34722% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -7370,17 +7392,17 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>98.400</t>
+          <t>30.333</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>2.406</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2.34375% por bloco, ~6 blocos</t>
+          <t>0.69444% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -7402,17 +7424,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>5,98 mi</t>
+          <t>1,17 mi</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>107.000</t>
+          <t>32.240</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>3.51562% por bloco, ~6 blocos</t>
+          <t>1.04167% por bloco, ~22 blocos</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -7434,12 +7456,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,70 mi</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>886.930</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -7466,17 +7488,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>124.000</t>
+          <t>11.400</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>188.000</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>0.00047% por bloco, ~64 blocos</t>
+          <t>0.00007% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -7498,17 +7520,17 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>0.00094% por bloco, ~64 blocos</t>
+          <t>0.00013% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -7530,17 +7552,17 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>0.00469% por bloco, ~64 blocos</t>
+          <t>0.00067% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -7562,17 +7584,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>0.02344% por bloco, ~64 blocos</t>
+          <t>0.00335% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7594,17 +7616,17 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>0.04688% por bloco, ~64 blocos</t>
+          <t>0.00670% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -7626,17 +7648,17 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>1.620</t>
+          <t>806</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>193</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>0.11719% por bloco, ~64 blocos</t>
+          <t>0.01674% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -7658,17 +7680,17 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>126.000</t>
+          <t>37.546</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>6.500</t>
+          <t>2.703</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>0.10714% por bloco, ~140 blocos</t>
+          <t>0.03348% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -7690,17 +7712,17 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>1,30 mi</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>35.110</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>0.08371% por bloco, ~269 blocos</t>
+          <t>0.05022% por bloco, ~448 blocos</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -7722,12 +7744,12 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,70 mi</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>886.914</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -7754,17 +7776,17 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>250.000</t>
+          <t>20.500</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>275.000</t>
+          <t>24.900</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>0.00043% por bloco, ~58 blocos</t>
+          <t>0.00023% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -7786,17 +7808,17 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>0.00087% por bloco, ~58 blocos</t>
+          <t>0.00046% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -7818,17 +7840,17 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>0.00434% por bloco, ~58 blocos</t>
+          <t>0.00231% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -7850,17 +7872,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>0.02170% por bloco, ~58 blocos</t>
+          <t>0.01157% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -7882,17 +7904,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>0.04340% por bloco, ~58 blocos</t>
+          <t>0.02315% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -7914,17 +7936,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>979</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>199</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>0.10851% por bloco, ~58 blocos</t>
+          <t>0.05787% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -7946,17 +7968,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>134.000</t>
+          <t>38.240</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>6.430</t>
+          <t>2.719</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>0.17361% por bloco, ~72 blocos</t>
+          <t>0.11574% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -7978,17 +8000,17 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>5,24 mi</t>
+          <t>1,23 mi</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>92.900</t>
+          <t>31.786</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>0.21701% por bloco, ~86 blocos</t>
+          <t>0.17361% por bloco, ~108 blocos</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -8010,12 +8032,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>5,24 mi</t>
+          <t>42,30 mi</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>92.900</t>
+          <t>739.944</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -8042,17 +8064,17 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>580.000</t>
+          <t>45.800</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>440.000</t>
+          <t>39.000</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>0.00016% por bloco, ~192 blocos</t>
+          <t>0.00004% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -8074,17 +8096,17 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>0.00031% por bloco, ~192 blocos</t>
+          <t>0.00008% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -8106,17 +8128,17 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>0.00156% por bloco, ~192 blocos</t>
+          <t>0.00039% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -8138,17 +8160,17 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>0.00781% por bloco, ~192 blocos</t>
+          <t>0.00195% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -8170,17 +8192,17 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>0.01562% por bloco, ~192 blocos</t>
+          <t>0.00391% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -8202,17 +8224,17 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>4.350</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>0.03906% por bloco, ~192 blocos</t>
+          <t>0.00977% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -8234,17 +8256,17 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>220.000</t>
+          <t>64.228</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>9.710</t>
+          <t>3.861</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>0.03906% por bloco, ~384 blocos</t>
+          <t>0.01953% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -8266,17 +8288,17 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>1,72 mi</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>42.600</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>0.04688% por bloco, ~480 blocos</t>
+          <t>0.02930% por bloco, ~768 blocos</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -8298,12 +8320,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,80 mi</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>887.942</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -8330,17 +8352,17 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>1,53 mi</t>
+          <t>113.000</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>761.000</t>
+          <t>65.000</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>0.00391% por bloco, ~6 blocos</t>
+          <t>0.00025% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -8362,17 +8384,17 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>0.00781% por bloco, ~6 blocos</t>
+          <t>0.00050% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -8394,17 +8416,17 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>0.03906% por bloco, ~6 blocos</t>
+          <t>0.00250% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -8426,17 +8448,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>0.19531% por bloco, ~6 blocos</t>
+          <t>0.01250% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -8458,17 +8480,17 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>323</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>0.39062% por bloco, ~6 blocos</t>
+          <t>0.02500% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -8490,17 +8512,17 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>6.940</t>
+          <t>2.893</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>0.97656% por bloco, ~6 blocos</t>
+          <t>0.06250% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -8522,17 +8544,17 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>296.000</t>
+          <t>79.156</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>11.300</t>
+          <t>4.452</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>0.57870% por bloco, ~22 blocos</t>
+          <t>0.12500% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -8554,17 +8576,17 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>5,24 mi</t>
+          <t>1,72 mi</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>92.900</t>
+          <t>40.510</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>0.36621% por bloco, ~51 blocos</t>
+          <t>0.18750% por bloco, ~100 blocos</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -8586,12 +8608,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>5,24 mi</t>
+          <t>42,30 mi</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>92.900</t>
+          <t>739.954</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -8618,17 +8640,17 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>3,78 mi</t>
+          <t>251.000</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>1,28 mi</t>
+          <t>104.000</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>0.00002% por bloco, ~1203 blocos</t>
+          <t>0.00001% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -8650,17 +8672,17 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>0.00005% por bloco, ~1203 blocos</t>
+          <t>0.00001% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -8682,17 +8704,17 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>0.00025% por bloco, ~1203 blocos</t>
+          <t>0.00006% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -8714,17 +8736,17 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>0.00125% por bloco, ~1203 blocos</t>
+          <t>0.00032% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -8746,17 +8768,17 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>1.850</t>
+          <t>921</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>0.00249% por bloco, ~1203 blocos</t>
+          <t>0.00063% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -8778,17 +8800,17 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>16.900</t>
+          <t>6.437</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>1.610</t>
+          <t>834</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>0.00623% por bloco, ~1203 blocos</t>
+          <t>0.00158% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -8810,17 +8832,17 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>543.000</t>
+          <t>136.294</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>18.300</t>
+          <t>6.816</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>0.00665% por bloco, ~2256 blocos</t>
+          <t>0.00317% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -8842,17 +8864,17 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>2,47 mi</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>55.648</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>0.00712% por bloco, ~3158 blocos</t>
+          <t>0.00475% por bloco, ~4738 blocos</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -8874,12 +8896,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,80 mi</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>888.936</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8906,17 +8928,17 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>13,70 mi</t>
+          <t>830.000</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>2,72 mi</t>
+          <t>210.000</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>0.00007% por bloco, ~400 blocos</t>
+          <t>0.00004% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -8938,17 +8960,17 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>959</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>0.00015% por bloco, ~400 blocos</t>
+          <t>0.00007% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -8970,17 +8992,17 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.055</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>0.00075% por bloco, ~400 blocos</t>
+          <t>0.00038% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -9002,17 +9024,17 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>1.660</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>0.00375% por bloco, ~400 blocos</t>
+          <t>0.00187% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -9034,17 +9056,17 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>7.010</t>
+          <t>2.872</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>499</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>0.00750% por bloco, ~400 blocos</t>
+          <t>0.00375% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -9066,17 +9088,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>46.700</t>
+          <t>16.300</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>0.01875% por bloco, ~400 blocos</t>
+          <t>0.00937% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -9098,17 +9120,17 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>1,01 mi</t>
+          <t>233.948</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>29.000</t>
+          <t>10.052</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>0.02679% por bloco, ~560 blocos</t>
+          <t>0.01875% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -9130,17 +9152,17 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>3,25 mi</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>68.184</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>0.03516% por bloco, ~640 blocos</t>
+          <t>0.02813% por bloco, ~800 blocos</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -9162,12 +9184,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,90 mi</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>888.930</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -9194,17 +9216,17 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>45,60 mi</t>
+          <t>2,49 mi</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>5,55 mi</t>
+          <t>407.000</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>0.00014% por bloco, ~216 blocos</t>
+          <t>0.00003% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -9226,17 +9248,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>8.170</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>562</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>0.00028% por bloco, ~216 blocos</t>
+          <t>0.00007% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -9258,17 +9280,17 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>8.890</t>
+          <t>3.778</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>1.050</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>0.00139% por bloco, ~216 blocos</t>
+          <t>0.00035% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -9290,17 +9312,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>14.500</t>
+          <t>5.684</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>1.460</t>
+          <t>756</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>0.00694% por bloco, ~216 blocos</t>
+          <t>0.00174% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -9322,17 +9344,17 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>25.900</t>
+          <t>9.084</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>2.160</t>
+          <t>1.083</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>0.01389% por bloco, ~216 blocos</t>
+          <t>0.00347% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -9354,17 +9376,17 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>137.000</t>
+          <t>40.054</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>6.900</t>
+          <t>2.866</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>0.03472% por bloco, ~216 blocos</t>
+          <t>0.00868% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -9386,17 +9408,17 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>2,05 mi</t>
+          <t>446.328</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>48.000</t>
+          <t>15.896</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>0.03720% por bloco, ~403 blocos</t>
+          <t>0.01736% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -9418,17 +9440,17 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>4,22 mi</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>83.160</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>0.03906% por bloco, ~576 blocos</t>
+          <t>0.02604% por bloco, ~864 blocos</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -9450,12 +9472,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,90 mi</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>889.964</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -9482,17 +9504,17 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>143,00 mi</t>
+          <t>6,87 mi</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>11,00 mi</t>
+          <t>757.000</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>0.00013% por bloco, ~240 blocos</t>
+          <t>0.00001% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -9514,17 +9536,17 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>34.300</t>
+          <t>11.700</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>1.280</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>0.00025% por bloco, ~240 blocos</t>
+          <t>0.00003% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -9546,17 +9568,17 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>36.900</t>
+          <t>12.676</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>1.344</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>0.00125% por bloco, ~240 blocos</t>
+          <t>0.00015% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -9578,17 +9600,17 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>55.100</t>
+          <t>18.624</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>1.750</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>0.00625% por bloco, ~240 blocos</t>
+          <t>0.00075% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -9610,17 +9632,17 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>92.300</t>
+          <t>28.456</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>5.210</t>
+          <t>2.298</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>0.01250% por bloco, ~240 blocos</t>
+          <t>0.00150% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -9642,17 +9664,17 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>389.000</t>
+          <t>102.408</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>14.400</t>
+          <t>5.616</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>0.03125% por bloco, ~240 blocos</t>
+          <t>0.00375% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -9674,17 +9696,17 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>3,86 mi</t>
+          <t>781.040</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>76.700</t>
+          <t>24.072</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>0.02251% por bloco, ~666 blocos</t>
+          <t>0.00750% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -9706,17 +9728,17 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>5,46 mi</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>100.536</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>0.02093% por bloco, ~1075 blocos</t>
+          <t>0.01125% por bloco, ~2000 blocos</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -9738,12 +9760,12 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>6,29 mi</t>
+          <t>50,90 mi</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>111.000</t>
+          <t>889.962</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -9770,12 +9792,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>423,00 mi</t>
+          <t>19,00 mi</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>21,20 mi</t>
+          <t>1,41 mi</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -9802,12 +9824,12 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>163.000</t>
+          <t>47.300</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>8.140</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -9834,12 +9856,12 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>173.000</t>
+          <t>49.788</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>8.510</t>
+          <t>3.618</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -9866,12 +9888,12 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>233.000</t>
+          <t>67.158</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>10.600</t>
+          <t>4.458</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -9898,12 +9920,12 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>366.000</t>
+          <t>99.304</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>14.400</t>
+          <t>5.796</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -9930,12 +9952,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>1,18 mi</t>
+          <t>271.792</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>33.800</t>
+          <t>11.948</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -9962,12 +9984,12 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>7,34 mi</t>
+          <t>1,58 mi</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>130.000</t>
+          <t>42.108</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -9994,12 +10016,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>7,34 mi</t>
+          <t>8,17 mi</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>130.000</t>
+          <t>142.544</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -10026,12 +10048,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>7,34 mi</t>
+          <t>59,50 mi</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>130.000</t>
+          <t>1,04 mi</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -10058,12 +10080,12 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>1,19 bi</t>
+          <t>50,60 mi</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>39,90 mi</t>
+          <t>2,58 mi</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -10090,12 +10112,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>644.000</t>
+          <t>160.000</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>21.600</t>
+          <t>8.160</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -10122,12 +10144,12 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>678.000</t>
+          <t>168.000</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>22.400</t>
+          <t>8.424</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -10154,12 +10176,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>874.000</t>
+          <t>208.950</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>27.000</t>
+          <t>9.858</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -10186,12 +10208,12 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>1,18 mi</t>
+          <t>271.720</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>33.800</t>
+          <t>11.956</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -10218,12 +10240,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>3,31 mi</t>
+          <t>692.064</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>71.100</t>
+          <t>22.904</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -10250,12 +10272,12 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>7,34 mi</t>
+          <t>2,88 mi</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>130.000</t>
+          <t>64.864</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -10282,12 +10304,12 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>7,34 mi</t>
+          <t>11,27 mi</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>130.000</t>
+          <t>197.336</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -10314,12 +10336,12 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>7,34 mi</t>
+          <t>59,50 mi</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>130.000</t>
+          <t>1,04 mi</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -10862,7 +10884,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -10877,12 +10899,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>1,17 mi</t>
+          <t>1,24 mi</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>47.600</t>
+          <t>64.000</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10921,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -10914,12 +10936,12 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1,80 mi</t>
+          <t>1,92 mi</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>13.600</t>
+          <t>18.300</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10958,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -10951,12 +10973,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>5,31 mi</t>
+          <t>5,80 mi</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>15.600</t>
+          <t>21.000</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10995,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -10988,12 +11010,12 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>8,24 mi</t>
+          <t>9,10 mi</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>46.900</t>
+          <t>63.000</t>
         </is>
       </c>
     </row>
@@ -11057,12 +11079,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>1,01 mi</t>
+          <t>1,08 mi</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>703.800</t>
+          <t>754.290</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11072,7 +11094,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>200.430</t>
+          <t>215.730</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -11099,32 +11121,32 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>+205%</t>
+          <t>+217%</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>3,07 mi</t>
+          <t>3,41 mi</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2,15 mi</t>
+          <t>2,39 mi</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1,38 mi</t>
+          <t>1,54 mi</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>611.312</t>
+          <t>683.864</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>460.550</t>
+          <t>513.540</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -11146,32 +11168,32 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>+854%</t>
+          <t>+922%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>9,60 mi</t>
+          <t>11,01 mi</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>6,71 mi</t>
+          <t>7,71 mi</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>4,32 mi</t>
+          <t>4,96 mi</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>1,91 mi</t>
+          <t>2,20 mi</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1,44 mi</t>
+          <t>1,66 mi</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -11193,32 +11215,32 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>+2918%</t>
+          <t>+3248%</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>30,35 mi</t>
+          <t>36,07 mi</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>21,24 mi</t>
+          <t>25,25 mi</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>13,67 mi</t>
+          <t>16,24 mi</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>6,05 mi</t>
+          <t>7,22 mi</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>4,56 mi</t>
+          <t>5,42 mi</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -11240,32 +11262,32 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>+9544%</t>
+          <t>+10997%</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>96,99 mi</t>
+          <t>119,54 mi</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>67,87 mi</t>
+          <t>83,70 mi</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>43,69 mi</t>
+          <t>53,82 mi</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>19,33 mi</t>
+          <t>23,94 mi</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>14,56 mi</t>
+          <t>17,98 mi</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -11287,32 +11309,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>+31083%</t>
+          <t>+37252%</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>313,59 mi</t>
+          <t>402,35 mi</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>219,47 mi</t>
+          <t>281,74 mi</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>141,26 mi</t>
+          <t>181,16 mi</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>62,50 mi</t>
+          <t>80,58 mi</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>47,09 mi</t>
+          <t>60,51 mi</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -11334,32 +11356,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>+102445%</t>
+          <t>+128063%</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>1,03 bi</t>
+          <t>1,38 bi</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>721,71 mi</t>
+          <t>966,72 mi</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>464,53 mi</t>
+          <t>621,59 mi</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>205,53 mi</t>
+          <t>276,49 mi</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>154,84 mi</t>
+          <t>207,62 mi</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -11381,32 +11403,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>+345088%</t>
+          <t>+432742%</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>3,47 bi</t>
+          <t>4,66 bi</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>2,43 bi</t>
+          <t>3,26 bi</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>1,56 bi</t>
+          <t>2,10 bi</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>691,86 mi</t>
+          <t>933,77 mi</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>521,23 mi</t>
+          <t>701,20 mi</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -11534,7 +11556,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>48.082</t>
+          <t>55.188</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11549,7 +11571,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>673.000</t>
+          <t>773.000</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -11581,7 +11603,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>96.163</t>
+          <t>110.376</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11596,7 +11618,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>769.000</t>
+          <t>883.000</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -11628,7 +11650,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>608.428</t>
+          <t>723.167</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11638,12 +11660,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>5,48 mi</t>
+          <t>6,51 mi</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -11675,7 +11697,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>912.642</t>
+          <t>1,08 mi</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11690,7 +11712,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>6,08 mi</t>
+          <t>7,23 mi</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -11722,7 +11744,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>3,89 mi</t>
+          <t>4,79 mi</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11737,7 +11759,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>21,40 mi</t>
+          <t>26,40 mi</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -11769,7 +11791,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>15,72 mi</t>
+          <t>20,17 mi</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11779,12 +11801,12 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>75,40 mi</t>
+          <t>96,80 mi</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -11816,7 +11838,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>18,86 mi</t>
+          <t>24,20 mi</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11831,7 +11853,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>81,70 mi</t>
+          <t>105,00 mi</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -11863,7 +11885,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>72,36 mi</t>
+          <t>96,89 mi</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11878,7 +11900,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>289,00 mi</t>
+          <t>388,00 mi</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -11910,7 +11932,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>87,86 mi</t>
+          <t>117,65 mi</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11925,7 +11947,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>465,00 mi</t>
+          <t>623,00 mi</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -11957,7 +11979,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>347,95 mi</t>
+          <t>467,47 mi</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11972,7 +11994,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1,67 bi</t>
+          <t>2,24 bi</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -12323,7 +12345,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2,65 mi</t>
+          <t>2,90 mi</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -12355,7 +12377,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>8,24 mi</t>
+          <t>9,31 mi</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -12387,7 +12409,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>25,90 mi</t>
+          <t>30,30 mi</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -12419,7 +12441,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>82,60 mi</t>
+          <t>100,00 mi</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -12451,7 +12473,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>265,00 mi</t>
+          <t>334,00 mi</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -12616,7 +12638,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>9,21 mi</t>
+          <t>10,20 mi</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12648,7 +12670,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>18,40 mi</t>
+          <t>20,80 mi</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12680,7 +12702,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>36,30 mi</t>
+          <t>42,00 mi</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12712,7 +12734,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>72,40 mi</t>
+          <t>85,30 mi</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12744,7 +12766,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>146,00 mi</t>
+          <t>177,00 mi</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12776,7 +12798,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>291,00 mi</t>
+          <t>359,00 mi</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12808,7 +12830,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>593,00 mi</t>
+          <t>750,00 mi</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12840,7 +12862,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>1,19 bi</t>
+          <t>1,55 bi</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12872,7 +12894,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>2,44 bi</t>
+          <t>3,25 bi</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12904,7 +12926,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>5,09 bi</t>
+          <t>6,84 bi</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
